--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,6 +792,3796 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131743179</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>769932</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7136863</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131742944</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>769885</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7136810</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre hack i gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131742582</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>769849</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7136743</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>barksprätt på död gran</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131743467</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>769963</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7136864</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131742096</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>769850</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7136789</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131743394</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>769961</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7136875</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131742131</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>769833</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7136772</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131742013</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>769831</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7136801</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131742766</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83106</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>769868</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7136788</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på barken av en gammal gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131743538</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>769968</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7136828</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131742897</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>769870</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7136806</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131743509</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>769959</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7136821</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131743168</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>769905</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7136813</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131743501</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>769947</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7136830</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131742463</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>769892</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7136788</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131742854</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>769873</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7136797</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131742307</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>769860</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7136813</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hå hackade i död gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131742285</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>769857</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7136809</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack i basen på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131742668</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91791</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>769835</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7136761</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131742744</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>769838</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7136761</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131743206</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>769939</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7136863</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131742542</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>769868</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7136747</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>hack i rotben på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131742606</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>769809</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7136745</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131741841</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>769719</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7136723</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131743102</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91791</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>769921</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7136855</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131742808</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>769862</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7136789</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Både äldre och färska hack i gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131742654</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>769835</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7136761</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>under en granlåga, även vedticka på samma substrat</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131742977</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>769900</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7136814</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>flera äldre hål hackade i gammal låga</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131743066</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>769920</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7136852</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska hål hackade i gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131743340</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>769948</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7136880</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131741958</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>769752</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7136742</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131741991</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>769823</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7136789</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>rikligt på flera träd</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131742487</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>769886</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7136746</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färska hål hackade i gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131743244</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>769944</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7136855</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>stort hål i död gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131743600</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>770015</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7136821</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>rikligt i många träd!</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,42 +1010,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131742582</v>
+        <v>131743467</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769849</v>
+        <v>769963</v>
       </c>
       <c r="R5" t="n">
-        <v>7136743</v>
+        <v>7136864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,15 +1093,16 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>barksprätt på död gran</t>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,42 +1121,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131743467</v>
+        <v>131742096</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>91848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769963</v>
+        <v>769850</v>
       </c>
       <c r="R6" t="n">
-        <v>7136864</v>
+        <v>7136789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,11 +1195,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131742096</v>
+        <v>131742582</v>
       </c>
       <c r="B7" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,26 +1233,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769850</v>
+        <v>769849</v>
       </c>
       <c r="R7" t="n">
-        <v>7136789</v>
+        <v>7136743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,13 +1303,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>barksprätt på död gran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131742854</v>
+        <v>131742307</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,30 +2429,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2460,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769873</v>
+        <v>769860</v>
       </c>
       <c r="R18" t="n">
-        <v>7136797</v>
+        <v>7136813</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,13 +2499,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hå hackade i död gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2523,7 +2528,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131742307</v>
+        <v>131742285</v>
       </c>
       <c r="B19" t="n">
         <v>57895</v>
@@ -2556,7 +2561,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2566,10 +2571,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769860</v>
+        <v>769857</v>
       </c>
       <c r="R19" t="n">
-        <v>7136813</v>
+        <v>7136809</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,7 +2611,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>hå hackade i död gran</t>
+          <t>hack i basen på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,42 +2638,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131742285</v>
+        <v>131742668</v>
       </c>
       <c r="B20" t="n">
-        <v>57895</v>
+        <v>91791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769857</v>
+        <v>769835</v>
       </c>
       <c r="R20" t="n">
-        <v>7136809</v>
+        <v>7136761</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,17 +2718,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hack i basen på gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2743,38 +2743,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131742668</v>
+        <v>131742854</v>
       </c>
       <c r="B21" t="n">
-        <v>91791</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769835</v>
+        <v>769873</v>
       </c>
       <c r="R21" t="n">
-        <v>7136761</v>
+        <v>7136797</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3058,42 +3058,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131742542</v>
+        <v>131743102</v>
       </c>
       <c r="B24" t="n">
-        <v>57895</v>
+        <v>91791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3101,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769868</v>
+        <v>769921</v>
       </c>
       <c r="R24" t="n">
-        <v>7136747</v>
+        <v>7136855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,17 +3138,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hack i rotben på gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3279,10 +3274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131741841</v>
+        <v>131742542</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,16 +3285,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3322,10 +3317,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769719</v>
+        <v>769868</v>
       </c>
       <c r="R26" t="n">
-        <v>7136723</v>
+        <v>7136747</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3362,7 +3357,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,41 +3384,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131743102</v>
+        <v>131741841</v>
       </c>
       <c r="B27" t="n">
-        <v>91791</v>
+        <v>57898</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3431,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769921</v>
+        <v>769719</v>
       </c>
       <c r="R27" t="n">
-        <v>7136855</v>
+        <v>7136723</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,13 +3465,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3714,42 +3714,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131742977</v>
+        <v>131743340</v>
       </c>
       <c r="B30" t="n">
-        <v>57895</v>
+        <v>99034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>769900</v>
+        <v>769948</v>
       </c>
       <c r="R30" t="n">
-        <v>7136814</v>
+        <v>7136880</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3795,17 +3795,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>flera äldre hål hackade i gammal låga</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3934,42 +3930,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131743340</v>
+        <v>131742977</v>
       </c>
       <c r="B32" t="n">
-        <v>99034</v>
+        <v>57895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3977,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769948</v>
+        <v>769900</v>
       </c>
       <c r="R32" t="n">
-        <v>7136880</v>
+        <v>7136814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4015,13 +4011,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>flera äldre hål hackade i gammal låga</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131741958</v>
+        <v>131741991</v>
       </c>
       <c r="B33" t="n">
         <v>79260</v>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769752</v>
+        <v>769823</v>
       </c>
       <c r="R33" t="n">
-        <v>7136742</v>
+        <v>7136789</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4118,6 +4118,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4145,7 +4150,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131741991</v>
+        <v>131741958</v>
       </c>
       <c r="B34" t="n">
         <v>79260</v>
@@ -4187,10 +4192,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769823</v>
+        <v>769752</v>
       </c>
       <c r="R34" t="n">
-        <v>7136789</v>
+        <v>7136742</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4223,11 +4228,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4255,7 +4255,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131742487</v>
+        <v>131743244</v>
       </c>
       <c r="B35" t="n">
         <v>57895</v>
@@ -4288,7 +4288,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769886</v>
+        <v>769944</v>
       </c>
       <c r="R35" t="n">
-        <v>7136746</v>
+        <v>7136855</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>stort hål i död gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,10 +4365,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131743244</v>
+        <v>131743600</v>
       </c>
       <c r="B36" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4376,31 +4376,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4408,10 +4407,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769944</v>
+        <v>770015</v>
       </c>
       <c r="R36" t="n">
-        <v>7136855</v>
+        <v>7136821</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4447,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>stort hål i död gran</t>
+          <t>rikligt i många träd!</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4457,6 +4456,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131743600</v>
+        <v>131742487</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,30 +4486,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4517,10 +4518,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>770015</v>
+        <v>769886</v>
       </c>
       <c r="R37" t="n">
-        <v>7136821</v>
+        <v>7136746</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4558,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>rikligt i många träd!</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4566,7 +4567,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4582,6 +4582,757 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131756063</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>770087</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7136820</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131756171</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>769855</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7136722</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>ringhack högt upp i gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131756083</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79261</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>770078</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7136818</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131756087</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>770078</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7136818</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131756067</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91792</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>770087</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7136820</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131755321</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>770055</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7136838</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>äldre ringhack högt upp på granstam</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131756135</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mjösjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>769898</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7136732</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131743179</v>
+        <v>131742944</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,30 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769932</v>
+        <v>769885</v>
       </c>
       <c r="R3" t="n">
-        <v>7136863</v>
+        <v>7136810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,13 +876,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre hack i gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131742944</v>
+        <v>131743179</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,31 +916,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769885</v>
+        <v>769932</v>
       </c>
       <c r="R4" t="n">
-        <v>7136810</v>
+        <v>7136863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,17 +985,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre hack i gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,42 +1010,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131743467</v>
+        <v>131742096</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>91849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769963</v>
+        <v>769850</v>
       </c>
       <c r="R5" t="n">
-        <v>7136864</v>
+        <v>7136789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131742096</v>
+        <v>131742582</v>
       </c>
       <c r="B6" t="n">
-        <v>91848</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,26 +1122,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769850</v>
+        <v>769849</v>
       </c>
       <c r="R6" t="n">
-        <v>7136789</v>
+        <v>7136743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,13 +1192,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>barksprätt på död gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1222,42 +1221,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131742582</v>
+        <v>131743467</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769849</v>
+        <v>769963</v>
       </c>
       <c r="R7" t="n">
-        <v>7136743</v>
+        <v>7136864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,15 +1304,16 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>barksprätt på död gran</t>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>131743394</v>
       </c>
       <c r="B8" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>131742131</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131742013</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131742766</v>
       </c>
       <c r="B11" t="n">
-        <v>83106</v>
+        <v>83107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>131743538</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131742897</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>131743509</v>
       </c>
       <c r="B14" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131743168</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>131743501</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>131742463</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131742307</v>
+        <v>131742854</v>
       </c>
       <c r="B18" t="n">
-        <v>57895</v>
+        <v>79261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,31 +2429,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769860</v>
+        <v>769873</v>
       </c>
       <c r="R18" t="n">
-        <v>7136813</v>
+        <v>7136797</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,17 +2498,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hå hackade i död gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2528,42 +2523,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131742285</v>
+        <v>131742668</v>
       </c>
       <c r="B19" t="n">
-        <v>57895</v>
+        <v>91792</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2571,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769857</v>
+        <v>769835</v>
       </c>
       <c r="R19" t="n">
-        <v>7136809</v>
+        <v>7136761</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,17 +2603,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>hack i basen på gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2638,41 +2628,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131742668</v>
+        <v>131742285</v>
       </c>
       <c r="B20" t="n">
-        <v>91791</v>
+        <v>57896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2680,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769835</v>
+        <v>769857</v>
       </c>
       <c r="R20" t="n">
-        <v>7136761</v>
+        <v>7136809</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,13 +2709,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack i basen på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2743,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131742854</v>
+        <v>131742307</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2754,30 +2749,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769873</v>
+        <v>769860</v>
       </c>
       <c r="R21" t="n">
-        <v>7136797</v>
+        <v>7136813</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,13 +2819,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>hå hackade i död gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>131742744</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>131743206</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>131743102</v>
       </c>
       <c r="B24" t="n">
-        <v>91791</v>
+        <v>91792</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,42 +3163,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131742606</v>
+        <v>131742542</v>
       </c>
       <c r="B25" t="n">
-        <v>99034</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769809</v>
+        <v>769868</v>
       </c>
       <c r="R25" t="n">
-        <v>7136745</v>
+        <v>7136747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3255,7 +3255,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3274,10 +3273,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131742542</v>
+        <v>131741841</v>
       </c>
       <c r="B26" t="n">
-        <v>57895</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3285,16 +3284,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3317,10 +3316,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769868</v>
+        <v>769719</v>
       </c>
       <c r="R26" t="n">
-        <v>7136747</v>
+        <v>7136723</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,7 +3356,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,42 +3383,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131741841</v>
+        <v>131742606</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3427,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769719</v>
+        <v>769809</v>
       </c>
       <c r="R27" t="n">
-        <v>7136723</v>
+        <v>7136745</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,7 +3466,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3476,6 +3475,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131742808</v>
+        <v>131742654</v>
       </c>
       <c r="B28" t="n">
-        <v>57895</v>
+        <v>91829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,31 +3505,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3537,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>769862</v>
+        <v>769835</v>
       </c>
       <c r="R28" t="n">
-        <v>7136789</v>
+        <v>7136761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,7 +3576,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Både äldre och färska hack i gran</t>
+          <t>under en granlåga, även vedticka på samma substrat</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,6 +3585,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131742654</v>
+        <v>131742808</v>
       </c>
       <c r="B29" t="n">
-        <v>91828</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,30 +3615,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3646,10 +3647,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>769835</v>
+        <v>769862</v>
       </c>
       <c r="R29" t="n">
-        <v>7136761</v>
+        <v>7136789</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,7 +3687,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>under en granlåga, även vedticka på samma substrat</t>
+          <t>Både äldre och färska hack i gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3695,7 +3696,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>131743340</v>
       </c>
       <c r="B30" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131743066</v>
+        <v>131742977</v>
       </c>
       <c r="B31" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769920</v>
+        <v>769900</v>
       </c>
       <c r="R31" t="n">
-        <v>7136852</v>
+        <v>7136814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>flera äldre hål hackade i gammal låga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131742977</v>
+        <v>131743066</v>
       </c>
       <c r="B32" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769900</v>
+        <v>769920</v>
       </c>
       <c r="R32" t="n">
-        <v>7136814</v>
+        <v>7136852</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>flera äldre hål hackade i gammal låga</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4043,7 +4043,7 @@
         <v>131741991</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>131741958</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131743244</v>
+        <v>131742487</v>
       </c>
       <c r="B35" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769944</v>
+        <v>769886</v>
       </c>
       <c r="R35" t="n">
-        <v>7136855</v>
+        <v>7136746</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>stort hål i död gran</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,10 +4365,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131743600</v>
+        <v>131743244</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4376,30 +4376,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4407,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>770015</v>
+        <v>769944</v>
       </c>
       <c r="R36" t="n">
-        <v>7136821</v>
+        <v>7136855</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4447,7 +4448,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>rikligt i många träd!</t>
+          <t>stort hål i död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4456,7 +4457,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131742487</v>
+        <v>131743600</v>
       </c>
       <c r="B37" t="n">
-        <v>57895</v>
+        <v>79261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,31 +4486,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4518,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769886</v>
+        <v>770015</v>
       </c>
       <c r="R37" t="n">
-        <v>7136746</v>
+        <v>7136821</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,7 +4557,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>rikligt i många träd!</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4567,6 +4566,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131742944</v>
+        <v>131743179</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,31 +806,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769885</v>
+        <v>769932</v>
       </c>
       <c r="R3" t="n">
-        <v>7136810</v>
+        <v>7136863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,17 +875,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>äldre hack i gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131743179</v>
+        <v>131742944</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,30 +911,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769932</v>
+        <v>769885</v>
       </c>
       <c r="R4" t="n">
-        <v>7136863</v>
+        <v>7136810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,13 +981,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre hack i gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131742096</v>
+        <v>131742582</v>
       </c>
       <c r="B5" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,26 +1021,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769850</v>
+        <v>769849</v>
       </c>
       <c r="R5" t="n">
-        <v>7136789</v>
+        <v>7136743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,13 +1091,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>barksprätt på död gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,42 +1120,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131742582</v>
+        <v>131743467</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769849</v>
+        <v>769963</v>
       </c>
       <c r="R6" t="n">
-        <v>7136743</v>
+        <v>7136864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,15 +1203,16 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>barksprätt på död gran</t>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,42 +1231,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131743467</v>
+        <v>131742096</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769963</v>
+        <v>769850</v>
       </c>
       <c r="R7" t="n">
-        <v>7136864</v>
+        <v>7136789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,42 +1332,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131743394</v>
+        <v>131742131</v>
       </c>
       <c r="B8" t="n">
-        <v>99035</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769961</v>
+        <v>769833</v>
       </c>
       <c r="R8" t="n">
-        <v>7136875</v>
+        <v>7136772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,13 +1413,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1438,42 +1442,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131742131</v>
+        <v>131743394</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769833</v>
+        <v>769961</v>
       </c>
       <c r="R9" t="n">
-        <v>7136772</v>
+        <v>7136875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,17 +1523,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>131742013</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131742766</v>
       </c>
       <c r="B11" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>131743538</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131742897</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>131743509</v>
       </c>
       <c r="B14" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131743168</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>131743501</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>131742463</v>
       </c>
       <c r="B17" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>131742854</v>
       </c>
       <c r="B18" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>131742668</v>
       </c>
       <c r="B19" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131742285</v>
+        <v>131742307</v>
       </c>
       <c r="B20" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769857</v>
+        <v>769860</v>
       </c>
       <c r="R20" t="n">
-        <v>7136809</v>
+        <v>7136813</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>hack i basen på gran</t>
+          <t>hå hackade i död gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131742307</v>
+        <v>131742285</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769860</v>
+        <v>769857</v>
       </c>
       <c r="R21" t="n">
-        <v>7136813</v>
+        <v>7136809</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>hå hackade i död gran</t>
+          <t>hack i basen på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,7 +2851,7 @@
         <v>131742744</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>131743206</v>
       </c>
       <c r="B23" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,41 +3058,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131743102</v>
+        <v>131742606</v>
       </c>
       <c r="B24" t="n">
-        <v>91792</v>
+        <v>99038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3100,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769921</v>
+        <v>769809</v>
       </c>
       <c r="R24" t="n">
-        <v>7136855</v>
+        <v>7136745</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,6 +3137,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3163,42 +3169,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131742542</v>
+        <v>131743102</v>
       </c>
       <c r="B25" t="n">
-        <v>57896</v>
+        <v>91795</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3206,10 +3211,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769868</v>
+        <v>769921</v>
       </c>
       <c r="R25" t="n">
-        <v>7136747</v>
+        <v>7136855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,17 +3249,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hack i rotben på gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3273,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131741841</v>
+        <v>131742542</v>
       </c>
       <c r="B26" t="n">
         <v>57899</v>
@@ -3284,16 +3285,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3316,10 +3317,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769719</v>
+        <v>769868</v>
       </c>
       <c r="R26" t="n">
-        <v>7136723</v>
+        <v>7136747</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,7 +3357,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,42 +3384,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131742606</v>
+        <v>131741841</v>
       </c>
       <c r="B27" t="n">
-        <v>99035</v>
+        <v>57902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3426,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769809</v>
+        <v>769719</v>
       </c>
       <c r="R27" t="n">
-        <v>7136745</v>
+        <v>7136723</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3467,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,7 +3476,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>131742654</v>
       </c>
       <c r="B28" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>131742808</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,42 +3714,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131743340</v>
+        <v>131743066</v>
       </c>
       <c r="B30" t="n">
-        <v>99035</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>769948</v>
+        <v>769920</v>
       </c>
       <c r="R30" t="n">
-        <v>7136880</v>
+        <v>7136852</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3795,13 +3795,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>färska hål hackade i gran</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3823,7 +3827,7 @@
         <v>131742977</v>
       </c>
       <c r="B31" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3930,42 +3934,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131743066</v>
+        <v>131743340</v>
       </c>
       <c r="B32" t="n">
-        <v>57896</v>
+        <v>99038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3973,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769920</v>
+        <v>769948</v>
       </c>
       <c r="R32" t="n">
-        <v>7136852</v>
+        <v>7136880</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4011,17 +4015,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska hål hackade i gran</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4040,10 +4040,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131741991</v>
+        <v>131741958</v>
       </c>
       <c r="B33" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769823</v>
+        <v>769752</v>
       </c>
       <c r="R33" t="n">
-        <v>7136789</v>
+        <v>7136742</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4118,11 +4118,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4150,10 +4145,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131741958</v>
+        <v>131741991</v>
       </c>
       <c r="B34" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,10 +4187,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769752</v>
+        <v>769823</v>
       </c>
       <c r="R34" t="n">
-        <v>7136742</v>
+        <v>7136789</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4228,6 +4223,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131742487</v>
+        <v>131743244</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769886</v>
+        <v>769944</v>
       </c>
       <c r="R35" t="n">
-        <v>7136746</v>
+        <v>7136855</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>stort hål i död gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,10 +4365,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131743244</v>
+        <v>131742487</v>
       </c>
       <c r="B36" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769944</v>
+        <v>769886</v>
       </c>
       <c r="R36" t="n">
-        <v>7136855</v>
+        <v>7136746</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>stort hål i död gran</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4478,7 +4478,7 @@
         <v>131743600</v>
       </c>
       <c r="B37" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>131756063</v>
       </c>
       <c r="B38" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>131756171</v>
       </c>
       <c r="B39" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>131756083</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>131756087</v>
       </c>
       <c r="B41" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>131756067</v>
       </c>
       <c r="B42" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>131755321</v>
       </c>
       <c r="B43" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>131756135</v>
       </c>
       <c r="B44" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -1120,42 +1120,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131743467</v>
+        <v>131742096</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>91852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769963</v>
+        <v>769850</v>
       </c>
       <c r="R6" t="n">
-        <v>7136864</v>
+        <v>7136789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,37 +1221,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131742096</v>
+        <v>131743467</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769850</v>
+        <v>769963</v>
       </c>
       <c r="R7" t="n">
-        <v>7136789</v>
+        <v>7136864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,6 +1300,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131743501</v>
+        <v>131742463</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,31 +2214,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2246,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>769947</v>
+        <v>769892</v>
       </c>
       <c r="R16" t="n">
-        <v>7136830</v>
+        <v>7136788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,17 +2283,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131742463</v>
+        <v>131743501</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,30 +2319,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2355,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>769892</v>
+        <v>769947</v>
       </c>
       <c r="R17" t="n">
-        <v>7136788</v>
+        <v>7136830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,13 +2389,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2418,38 +2418,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131742854</v>
+        <v>131742668</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769873</v>
+        <v>769835</v>
       </c>
       <c r="R18" t="n">
-        <v>7136797</v>
+        <v>7136761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,38 +2523,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131742668</v>
+        <v>131742854</v>
       </c>
       <c r="B19" t="n">
-        <v>91795</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769835</v>
+        <v>769873</v>
       </c>
       <c r="R19" t="n">
-        <v>7136761</v>
+        <v>7136797</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3058,42 +3058,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131742606</v>
+        <v>131743102</v>
       </c>
       <c r="B24" t="n">
-        <v>99038</v>
+        <v>91795</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3101,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769809</v>
+        <v>769921</v>
       </c>
       <c r="R24" t="n">
-        <v>7136745</v>
+        <v>7136855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3137,11 +3136,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,41 +3163,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131743102</v>
+        <v>131741841</v>
       </c>
       <c r="B25" t="n">
-        <v>91795</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3211,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769921</v>
+        <v>769719</v>
       </c>
       <c r="R25" t="n">
-        <v>7136855</v>
+        <v>7136723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,13 +3244,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3384,42 +3383,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131741841</v>
+        <v>131742606</v>
       </c>
       <c r="B27" t="n">
-        <v>57902</v>
+        <v>99038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3427,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769719</v>
+        <v>769809</v>
       </c>
       <c r="R27" t="n">
-        <v>7136723</v>
+        <v>7136745</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,7 +3466,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3476,6 +3475,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3824,42 +3824,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131742977</v>
+        <v>131743340</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769900</v>
+        <v>769948</v>
       </c>
       <c r="R31" t="n">
-        <v>7136814</v>
+        <v>7136880</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3905,17 +3905,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>flera äldre hål hackade i gammal låga</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3934,42 +3930,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131743340</v>
+        <v>131742977</v>
       </c>
       <c r="B32" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3977,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769948</v>
+        <v>769900</v>
       </c>
       <c r="R32" t="n">
-        <v>7136880</v>
+        <v>7136814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4015,13 +4011,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>flera äldre hål hackade i gammal låga</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131741958</v>
+        <v>131741991</v>
       </c>
       <c r="B33" t="n">
         <v>79264</v>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769752</v>
+        <v>769823</v>
       </c>
       <c r="R33" t="n">
-        <v>7136742</v>
+        <v>7136789</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4118,6 +4118,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4145,7 +4150,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131741991</v>
+        <v>131741958</v>
       </c>
       <c r="B34" t="n">
         <v>79264</v>
@@ -4187,10 +4192,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769823</v>
+        <v>769752</v>
       </c>
       <c r="R34" t="n">
-        <v>7136789</v>
+        <v>7136742</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4223,11 +4228,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131743244</v>
+        <v>131743600</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4266,31 +4266,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4298,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769944</v>
+        <v>770015</v>
       </c>
       <c r="R35" t="n">
-        <v>7136855</v>
+        <v>7136821</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,7 +4337,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>stort hål i död gran</t>
+          <t>rikligt i många träd!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4347,6 +4346,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131742487</v>
+        <v>131743244</v>
       </c>
       <c r="B36" t="n">
         <v>57899</v>
@@ -4398,7 +4398,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769886</v>
+        <v>769944</v>
       </c>
       <c r="R36" t="n">
-        <v>7136746</v>
+        <v>7136855</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>stort hål i död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4475,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131743600</v>
+        <v>131742487</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,30 +4486,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4517,10 +4518,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>770015</v>
+        <v>769886</v>
       </c>
       <c r="R37" t="n">
-        <v>7136821</v>
+        <v>7136746</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4558,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>rikligt i många träd!</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4566,7 +4567,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131742582</v>
+        <v>131742096</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,31 +1021,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769849</v>
+        <v>769850</v>
       </c>
       <c r="R5" t="n">
-        <v>7136743</v>
+        <v>7136789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,17 +1086,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>barksprätt på död gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131742096</v>
+        <v>131742582</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,26 +1122,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769850</v>
+        <v>769849</v>
       </c>
       <c r="R6" t="n">
-        <v>7136789</v>
+        <v>7136743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,13 +1192,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>barksprätt på död gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131742463</v>
+        <v>131743501</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,30 +2214,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>769892</v>
+        <v>769947</v>
       </c>
       <c r="R16" t="n">
-        <v>7136788</v>
+        <v>7136830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,13 +2284,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2308,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131743501</v>
+        <v>131742463</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,31 +2324,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2351,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>769947</v>
+        <v>769892</v>
       </c>
       <c r="R17" t="n">
-        <v>7136830</v>
+        <v>7136788</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,17 +2393,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2418,41 +2418,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131742668</v>
+        <v>131742285</v>
       </c>
       <c r="B18" t="n">
-        <v>91795</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2460,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769835</v>
+        <v>769857</v>
       </c>
       <c r="R18" t="n">
-        <v>7136761</v>
+        <v>7136809</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,13 +2499,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i basen på gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2523,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131742854</v>
+        <v>131742307</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,30 +2539,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2565,10 +2571,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769873</v>
+        <v>769860</v>
       </c>
       <c r="R19" t="n">
-        <v>7136797</v>
+        <v>7136813</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,13 +2609,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hå hackade i död gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2628,42 +2638,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131742307</v>
+        <v>131742668</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2671,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769860</v>
+        <v>769835</v>
       </c>
       <c r="R20" t="n">
-        <v>7136813</v>
+        <v>7136761</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,17 +2718,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hå hackade i död gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2738,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131742285</v>
+        <v>131742854</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,31 +2754,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769857</v>
+        <v>769873</v>
       </c>
       <c r="R21" t="n">
-        <v>7136809</v>
+        <v>7136797</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,17 +2823,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>hack i basen på gran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131742654</v>
+        <v>131742808</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>57899</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,30 +3505,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3536,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>769835</v>
+        <v>769862</v>
       </c>
       <c r="R28" t="n">
-        <v>7136761</v>
+        <v>7136789</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3576,7 +3577,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>under en granlåga, även vedticka på samma substrat</t>
+          <t>Både äldre och färska hack i gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3585,7 +3586,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131742808</v>
+        <v>131742654</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>91832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,31 +3615,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3647,10 +3646,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>769862</v>
+        <v>769835</v>
       </c>
       <c r="R29" t="n">
-        <v>7136789</v>
+        <v>7136761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3686,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Både äldre och färska hack i gran</t>
+          <t>under en granlåga, även vedticka på samma substrat</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,6 +3695,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131743066</v>
+        <v>131742977</v>
       </c>
       <c r="B30" t="n">
         <v>57899</v>
@@ -3747,7 +3747,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>769920</v>
+        <v>769900</v>
       </c>
       <c r="R30" t="n">
-        <v>7136852</v>
+        <v>7136814</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>flera äldre hål hackade i gammal låga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3824,42 +3824,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131743340</v>
+        <v>131743066</v>
       </c>
       <c r="B31" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769948</v>
+        <v>769920</v>
       </c>
       <c r="R31" t="n">
-        <v>7136880</v>
+        <v>7136852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3905,13 +3905,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska hål hackade i gran</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3930,42 +3934,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131742977</v>
+        <v>131743340</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3973,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769900</v>
+        <v>769948</v>
       </c>
       <c r="R32" t="n">
-        <v>7136814</v>
+        <v>7136880</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4011,17 +4015,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>flera äldre hål hackade i gammal låga</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131743600</v>
+        <v>131742487</v>
       </c>
       <c r="B35" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4266,30 +4266,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4297,10 +4298,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>770015</v>
+        <v>769886</v>
       </c>
       <c r="R35" t="n">
-        <v>7136821</v>
+        <v>7136746</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4337,7 +4338,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>rikligt i många träd!</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4346,7 +4347,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131742487</v>
+        <v>131743600</v>
       </c>
       <c r="B37" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,31 +4486,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4518,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769886</v>
+        <v>770015</v>
       </c>
       <c r="R37" t="n">
-        <v>7136746</v>
+        <v>7136821</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,7 +4557,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>rikligt i många träd!</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4567,6 +4566,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131742808</v>
+        <v>131742654</v>
       </c>
       <c r="B28" t="n">
-        <v>57899</v>
+        <v>91832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,31 +3505,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3537,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>769862</v>
+        <v>769835</v>
       </c>
       <c r="R28" t="n">
-        <v>7136789</v>
+        <v>7136761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,7 +3576,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Både äldre och färska hack i gran</t>
+          <t>under en granlåga, även vedticka på samma substrat</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,6 +3585,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131742654</v>
+        <v>131742808</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,30 +3615,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3646,10 +3647,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>769835</v>
+        <v>769862</v>
       </c>
       <c r="R29" t="n">
-        <v>7136761</v>
+        <v>7136789</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,7 +3687,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>under en granlåga, även vedticka på samma substrat</t>
+          <t>Både äldre och färska hack i gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3695,7 +3696,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131743179</v>
+        <v>131742944</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,30 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769932</v>
+        <v>769885</v>
       </c>
       <c r="R3" t="n">
-        <v>7136863</v>
+        <v>7136810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,13 +876,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre hack i gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131742944</v>
+        <v>131743179</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,31 +916,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769885</v>
+        <v>769932</v>
       </c>
       <c r="R4" t="n">
-        <v>7136810</v>
+        <v>7136863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,17 +985,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre hack i gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,37 +1010,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131742096</v>
+        <v>131743467</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769850</v>
+        <v>769963</v>
       </c>
       <c r="R5" t="n">
-        <v>7136789</v>
+        <v>7136864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1089,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131742582</v>
+        <v>131742096</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,31 +1132,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769849</v>
+        <v>769850</v>
       </c>
       <c r="R6" t="n">
-        <v>7136743</v>
+        <v>7136789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,17 +1197,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>barksprätt på död gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,42 +1222,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131743467</v>
+        <v>131742582</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769963</v>
+        <v>769849</v>
       </c>
       <c r="R7" t="n">
-        <v>7136864</v>
+        <v>7136743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,16 +1305,15 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt med bladrosetter!</t>
+          <t>barksprätt på död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,42 +1332,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131742131</v>
+        <v>131743394</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>99044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769833</v>
+        <v>769961</v>
       </c>
       <c r="R8" t="n">
-        <v>7136772</v>
+        <v>7136875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,17 +1413,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,42 +1438,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131743394</v>
+        <v>131742131</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769961</v>
+        <v>769833</v>
       </c>
       <c r="R9" t="n">
-        <v>7136875</v>
+        <v>7136772</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,13 +1519,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>131742013</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131742766</v>
       </c>
       <c r="B11" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>131743538</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131742897</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>131743509</v>
       </c>
       <c r="B14" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131743168</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131743501</v>
+        <v>131742463</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,31 +2214,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2246,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>769947</v>
+        <v>769892</v>
       </c>
       <c r="R16" t="n">
-        <v>7136830</v>
+        <v>7136788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,17 +2283,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131742463</v>
+        <v>131743501</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,30 +2319,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2355,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>769892</v>
+        <v>769947</v>
       </c>
       <c r="R17" t="n">
-        <v>7136788</v>
+        <v>7136830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,13 +2389,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2418,42 +2418,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131742285</v>
+        <v>131742668</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>91801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769857</v>
+        <v>769835</v>
       </c>
       <c r="R18" t="n">
-        <v>7136809</v>
+        <v>7136761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,17 +2498,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i basen på gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2528,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131742307</v>
+        <v>131742854</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,31 +2534,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2571,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769860</v>
+        <v>769873</v>
       </c>
       <c r="R19" t="n">
-        <v>7136813</v>
+        <v>7136797</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,17 +2603,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>hå hackade i död gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2638,41 +2628,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131742668</v>
+        <v>131742285</v>
       </c>
       <c r="B20" t="n">
-        <v>91795</v>
+        <v>57901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2680,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769835</v>
+        <v>769857</v>
       </c>
       <c r="R20" t="n">
-        <v>7136761</v>
+        <v>7136809</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,13 +2709,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack i basen på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2743,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131742854</v>
+        <v>131742307</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2754,30 +2749,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769873</v>
+        <v>769860</v>
       </c>
       <c r="R21" t="n">
-        <v>7136797</v>
+        <v>7136813</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,13 +2819,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>hå hackade i död gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>131742744</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>131743206</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,41 +3058,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131743102</v>
+        <v>131742606</v>
       </c>
       <c r="B24" t="n">
-        <v>91795</v>
+        <v>99044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3100,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769921</v>
+        <v>769809</v>
       </c>
       <c r="R24" t="n">
-        <v>7136855</v>
+        <v>7136745</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,6 +3137,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3163,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131741841</v>
+        <v>131742542</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>57901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,16 +3180,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3206,10 +3212,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769719</v>
+        <v>769868</v>
       </c>
       <c r="R25" t="n">
-        <v>7136723</v>
+        <v>7136747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,7 +3252,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131742542</v>
+        <v>131741841</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3284,16 +3290,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3316,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769868</v>
+        <v>769719</v>
       </c>
       <c r="R26" t="n">
-        <v>7136747</v>
+        <v>7136723</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,7 +3362,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,42 +3389,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131742606</v>
+        <v>131743102</v>
       </c>
       <c r="B27" t="n">
-        <v>99038</v>
+        <v>91801</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3426,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769809</v>
+        <v>769921</v>
       </c>
       <c r="R27" t="n">
-        <v>7136745</v>
+        <v>7136855</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,11 +3467,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,7 +3497,7 @@
         <v>131742654</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>131742808</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131742977</v>
+        <v>131743066</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>769900</v>
+        <v>769920</v>
       </c>
       <c r="R30" t="n">
-        <v>7136814</v>
+        <v>7136852</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>flera äldre hål hackade i gammal låga</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3824,10 +3824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131743066</v>
+        <v>131742977</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769920</v>
+        <v>769900</v>
       </c>
       <c r="R31" t="n">
-        <v>7136852</v>
+        <v>7136814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>flera äldre hål hackade i gammal låga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3937,7 +3937,7 @@
         <v>131743340</v>
       </c>
       <c r="B32" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>131741991</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>131741958</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131742487</v>
+        <v>131743600</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4266,31 +4266,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4298,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769886</v>
+        <v>770015</v>
       </c>
       <c r="R35" t="n">
-        <v>7136746</v>
+        <v>7136821</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,7 +4337,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>rikligt i många träd!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4347,6 +4346,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>131743244</v>
       </c>
       <c r="B36" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131743600</v>
+        <v>131742487</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,30 +4486,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4517,10 +4518,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>770015</v>
+        <v>769886</v>
       </c>
       <c r="R37" t="n">
-        <v>7136821</v>
+        <v>7136746</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4558,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>rikligt i många träd!</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4566,7 +4567,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>131756063</v>
       </c>
       <c r="B38" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>131756171</v>
       </c>
       <c r="B39" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>131756083</v>
       </c>
       <c r="B40" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>131756087</v>
       </c>
       <c r="B41" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>131756067</v>
       </c>
       <c r="B42" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>131755321</v>
       </c>
       <c r="B43" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>131756135</v>
       </c>
       <c r="B44" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -1010,42 +1010,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131743467</v>
+        <v>131742582</v>
       </c>
       <c r="B5" t="n">
-        <v>99044</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769963</v>
+        <v>769849</v>
       </c>
       <c r="R5" t="n">
-        <v>7136864</v>
+        <v>7136743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,16 +1093,15 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt med bladrosetter!</t>
+          <t>barksprätt på död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,37 +1120,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131742096</v>
+        <v>131743467</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769850</v>
+        <v>769963</v>
       </c>
       <c r="R6" t="n">
-        <v>7136789</v>
+        <v>7136864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1199,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131742582</v>
+        <v>131742096</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,31 +1242,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769849</v>
+        <v>769850</v>
       </c>
       <c r="R7" t="n">
-        <v>7136743</v>
+        <v>7136789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,17 +1307,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>barksprätt på död gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2418,41 +2418,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131742668</v>
+        <v>131742285</v>
       </c>
       <c r="B18" t="n">
-        <v>91801</v>
+        <v>57901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2460,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769835</v>
+        <v>769857</v>
       </c>
       <c r="R18" t="n">
-        <v>7136761</v>
+        <v>7136809</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,13 +2499,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i basen på gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2628,42 +2633,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131742285</v>
+        <v>131742668</v>
       </c>
       <c r="B20" t="n">
-        <v>57901</v>
+        <v>91801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2671,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769857</v>
+        <v>769835</v>
       </c>
       <c r="R20" t="n">
-        <v>7136809</v>
+        <v>7136761</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,17 +2713,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hack i basen på gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3058,42 +3058,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131742606</v>
+        <v>131742542</v>
       </c>
       <c r="B24" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769809</v>
+        <v>769868</v>
       </c>
       <c r="R24" t="n">
-        <v>7136745</v>
+        <v>7136747</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,7 +3150,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3169,42 +3168,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131742542</v>
+        <v>131743102</v>
       </c>
       <c r="B25" t="n">
-        <v>57901</v>
+        <v>91801</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3212,10 +3210,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769868</v>
+        <v>769921</v>
       </c>
       <c r="R25" t="n">
-        <v>7136747</v>
+        <v>7136855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,17 +3248,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hack i rotben på gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3389,41 +3383,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131743102</v>
+        <v>131742606</v>
       </c>
       <c r="B27" t="n">
-        <v>91801</v>
+        <v>99044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3431,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769921</v>
+        <v>769809</v>
       </c>
       <c r="R27" t="n">
-        <v>7136855</v>
+        <v>7136745</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,6 +3462,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -2418,42 +2418,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131742285</v>
+        <v>131742668</v>
       </c>
       <c r="B18" t="n">
-        <v>57901</v>
+        <v>91801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769857</v>
+        <v>769835</v>
       </c>
       <c r="R18" t="n">
-        <v>7136809</v>
+        <v>7136761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,17 +2498,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i basen på gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2633,41 +2628,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131742668</v>
+        <v>131742285</v>
       </c>
       <c r="B20" t="n">
-        <v>91801</v>
+        <v>57901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769835</v>
+        <v>769857</v>
       </c>
       <c r="R20" t="n">
-        <v>7136761</v>
+        <v>7136809</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,13 +2709,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack i basen på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131742654</v>
+        <v>131742808</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>57901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,30 +3505,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3536,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>769835</v>
+        <v>769862</v>
       </c>
       <c r="R28" t="n">
-        <v>7136761</v>
+        <v>7136789</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3576,7 +3577,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>under en granlåga, även vedticka på samma substrat</t>
+          <t>Både äldre och färska hack i gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3585,7 +3586,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131742808</v>
+        <v>131742654</v>
       </c>
       <c r="B29" t="n">
-        <v>57901</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,31 +3615,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3647,10 +3646,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>769862</v>
+        <v>769835</v>
       </c>
       <c r="R29" t="n">
-        <v>7136789</v>
+        <v>7136761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3687,7 +3686,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Både äldre och färska hack i gran</t>
+          <t>under en granlåga, även vedticka på samma substrat</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,6 +3695,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -3058,42 +3058,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131742542</v>
+        <v>131743102</v>
       </c>
       <c r="B24" t="n">
-        <v>57901</v>
+        <v>91801</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3101,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769868</v>
+        <v>769921</v>
       </c>
       <c r="R24" t="n">
-        <v>7136747</v>
+        <v>7136855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,17 +3138,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hack i rotben på gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3168,41 +3163,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131743102</v>
+        <v>131742606</v>
       </c>
       <c r="B25" t="n">
-        <v>91801</v>
+        <v>99044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3210,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769921</v>
+        <v>769809</v>
       </c>
       <c r="R25" t="n">
-        <v>7136855</v>
+        <v>7136745</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,6 +3242,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,10 +3274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131741841</v>
+        <v>131742542</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>57901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3284,16 +3285,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3316,10 +3317,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769719</v>
+        <v>769868</v>
       </c>
       <c r="R26" t="n">
-        <v>7136723</v>
+        <v>7136747</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,7 +3357,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,42 +3384,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131742606</v>
+        <v>131741841</v>
       </c>
       <c r="B27" t="n">
-        <v>99044</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3426,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769809</v>
+        <v>769719</v>
       </c>
       <c r="R27" t="n">
-        <v>7136745</v>
+        <v>7136723</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3467,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,7 +3476,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131742808</v>
+        <v>131742654</v>
       </c>
       <c r="B28" t="n">
-        <v>57901</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,31 +3505,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3537,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>769862</v>
+        <v>769835</v>
       </c>
       <c r="R28" t="n">
-        <v>7136789</v>
+        <v>7136761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,7 +3576,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Både äldre och färska hack i gran</t>
+          <t>under en granlåga, även vedticka på samma substrat</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,6 +3585,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131742654</v>
+        <v>131742808</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>57901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,30 +3615,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3646,10 +3647,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>769835</v>
+        <v>769862</v>
       </c>
       <c r="R29" t="n">
-        <v>7136761</v>
+        <v>7136789</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,7 +3687,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>under en granlåga, även vedticka på samma substrat</t>
+          <t>Både äldre och färska hack i gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3695,7 +3696,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131743179</v>
+        <v>131742944</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,30 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769932</v>
+        <v>769885</v>
       </c>
       <c r="R3" t="n">
-        <v>7136863</v>
+        <v>7136810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,13 +876,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre hack i gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131742944</v>
+        <v>131743179</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,31 +916,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769885</v>
+        <v>769932</v>
       </c>
       <c r="R4" t="n">
-        <v>7136810</v>
+        <v>7136863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,17 +985,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre hack i gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,42 +1010,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131743467</v>
+        <v>131742582</v>
       </c>
       <c r="B5" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769963</v>
+        <v>769849</v>
       </c>
       <c r="R5" t="n">
-        <v>7136864</v>
+        <v>7136743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,16 +1093,15 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt med bladrosetter!</t>
+          <t>barksprätt på död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,37 +1120,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131742096</v>
+        <v>131743467</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>99098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769850</v>
+        <v>769963</v>
       </c>
       <c r="R6" t="n">
-        <v>7136789</v>
+        <v>7136864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1199,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131742582</v>
+        <v>131742096</v>
       </c>
       <c r="B7" t="n">
-        <v>57948</v>
+        <v>91912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,31 +1242,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769849</v>
+        <v>769850</v>
       </c>
       <c r="R7" t="n">
-        <v>7136743</v>
+        <v>7136789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,17 +1307,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>barksprätt på död gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,42 +1332,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131743394</v>
+        <v>131742131</v>
       </c>
       <c r="B8" t="n">
-        <v>99095</v>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769961</v>
+        <v>769833</v>
       </c>
       <c r="R8" t="n">
-        <v>7136875</v>
+        <v>7136772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,13 +1413,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1438,42 +1442,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131742131</v>
+        <v>131743394</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769833</v>
+        <v>769961</v>
       </c>
       <c r="R9" t="n">
-        <v>7136772</v>
+        <v>7136875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,17 +1523,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>131742766</v>
       </c>
       <c r="B11" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>131742897</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>131743509</v>
       </c>
       <c r="B14" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131743168</v>
       </c>
       <c r="B15" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>131742463</v>
       </c>
       <c r="B16" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>131742668</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131742854</v>
+        <v>131742307</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,30 +2534,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2565,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769873</v>
+        <v>769860</v>
       </c>
       <c r="R19" t="n">
-        <v>7136797</v>
+        <v>7136813</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,13 +2604,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hå hackade i död gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2738,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131742307</v>
+        <v>131742854</v>
       </c>
       <c r="B21" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,31 +2754,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769860</v>
+        <v>769873</v>
       </c>
       <c r="R21" t="n">
-        <v>7136813</v>
+        <v>7136797</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,17 +2823,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>hå hackade i död gran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>131742744</v>
       </c>
       <c r="B22" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>131743206</v>
       </c>
       <c r="B23" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,42 +3058,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131741841</v>
+        <v>131743102</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3101,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769719</v>
+        <v>769921</v>
       </c>
       <c r="R24" t="n">
-        <v>7136723</v>
+        <v>7136855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,17 +3138,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3168,41 +3163,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131743102</v>
+        <v>131742542</v>
       </c>
       <c r="B25" t="n">
-        <v>91852</v>
+        <v>57945</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3210,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769921</v>
+        <v>769868</v>
       </c>
       <c r="R25" t="n">
-        <v>7136855</v>
+        <v>7136747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,13 +3244,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hack i rotben på gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3273,42 +3273,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131742542</v>
+        <v>131742606</v>
       </c>
       <c r="B26" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769868</v>
+        <v>769809</v>
       </c>
       <c r="R26" t="n">
-        <v>7136747</v>
+        <v>7136745</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,6 +3365,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3383,42 +3384,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131742606</v>
+        <v>131741841</v>
       </c>
       <c r="B27" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3426,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769809</v>
+        <v>769719</v>
       </c>
       <c r="R27" t="n">
-        <v>7136745</v>
+        <v>7136723</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3467,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,7 +3476,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>131742654</v>
       </c>
       <c r="B28" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131742977</v>
+        <v>131743066</v>
       </c>
       <c r="B30" t="n">
         <v>57945</v>
@@ -3747,7 +3747,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>769900</v>
+        <v>769920</v>
       </c>
       <c r="R30" t="n">
-        <v>7136814</v>
+        <v>7136852</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>flera äldre hål hackade i gammal låga</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3824,7 +3824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131743066</v>
+        <v>131742977</v>
       </c>
       <c r="B31" t="n">
         <v>57945</v>
@@ -3857,7 +3857,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769920</v>
+        <v>769900</v>
       </c>
       <c r="R31" t="n">
-        <v>7136852</v>
+        <v>7136814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>flera äldre hål hackade i gammal låga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3937,7 +3937,7 @@
         <v>131743340</v>
       </c>
       <c r="B32" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>131741991</v>
       </c>
       <c r="B33" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>131741958</v>
       </c>
       <c r="B34" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131742487</v>
+        <v>131743600</v>
       </c>
       <c r="B35" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4266,31 +4266,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4298,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769886</v>
+        <v>770015</v>
       </c>
       <c r="R35" t="n">
-        <v>7136746</v>
+        <v>7136821</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,7 +4337,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>färska hål hackade i gran</t>
+          <t>rikligt i många träd!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4347,6 +4346,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131743600</v>
+        <v>131742487</v>
       </c>
       <c r="B37" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,30 +4486,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4517,10 +4518,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>770015</v>
+        <v>769886</v>
       </c>
       <c r="R37" t="n">
-        <v>7136821</v>
+        <v>7136746</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4558,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>rikligt i många träd!</t>
+          <t>färska hål hackade i gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4566,7 +4567,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>131756063</v>
       </c>
       <c r="B38" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>131756083</v>
       </c>
       <c r="B40" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>131756067</v>
       </c>
       <c r="B42" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131742944</v>
+        <v>131743179</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,31 +806,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769885</v>
+        <v>769932</v>
       </c>
       <c r="R3" t="n">
-        <v>7136810</v>
+        <v>7136863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,17 +875,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>äldre hack i gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131743179</v>
+        <v>131742944</v>
       </c>
       <c r="B4" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,30 +911,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769932</v>
+        <v>769885</v>
       </c>
       <c r="R4" t="n">
-        <v>7136863</v>
+        <v>7136810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,13 +981,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre hack i gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1332,42 +1332,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131742131</v>
+        <v>131743394</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769833</v>
+        <v>769961</v>
       </c>
       <c r="R8" t="n">
-        <v>7136772</v>
+        <v>7136875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,17 +1413,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,42 +1438,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131743394</v>
+        <v>131742131</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769961</v>
+        <v>769833</v>
       </c>
       <c r="R9" t="n">
-        <v>7136875</v>
+        <v>7136772</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,13 +1519,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131742463</v>
+        <v>131743501</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,30 +2214,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>769892</v>
+        <v>769947</v>
       </c>
       <c r="R16" t="n">
-        <v>7136788</v>
+        <v>7136830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,13 +2284,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2308,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131743501</v>
+        <v>131742463</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,31 +2324,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2351,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>769947</v>
+        <v>769892</v>
       </c>
       <c r="R17" t="n">
-        <v>7136830</v>
+        <v>7136788</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,17 +2393,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3058,41 +3058,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131743102</v>
+        <v>131741841</v>
       </c>
       <c r="B24" t="n">
-        <v>91855</v>
+        <v>57948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3100,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769921</v>
+        <v>769719</v>
       </c>
       <c r="R24" t="n">
-        <v>7136855</v>
+        <v>7136723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,13 +3139,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3163,42 +3168,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131742542</v>
+        <v>131743102</v>
       </c>
       <c r="B25" t="n">
-        <v>57945</v>
+        <v>91855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3206,10 +3210,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769868</v>
+        <v>769921</v>
       </c>
       <c r="R25" t="n">
-        <v>7136747</v>
+        <v>7136855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,17 +3248,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hack i rotben på gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3273,42 +3273,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131742606</v>
+        <v>131742542</v>
       </c>
       <c r="B26" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769809</v>
+        <v>769868</v>
       </c>
       <c r="R26" t="n">
-        <v>7136745</v>
+        <v>7136747</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
+          <t>hack i rotben på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,7 +3365,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3384,42 +3383,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131741841</v>
+        <v>131742606</v>
       </c>
       <c r="B27" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3427,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769719</v>
+        <v>769809</v>
       </c>
       <c r="R27" t="n">
-        <v>7136723</v>
+        <v>7136745</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,7 +3466,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3476,6 +3475,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11302-2026 artfynd.xlsx
+++ b/artfynd/A 11302-2026 artfynd.xlsx
@@ -1332,42 +1332,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131743394</v>
+        <v>131742131</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769961</v>
+        <v>769833</v>
       </c>
       <c r="R8" t="n">
-        <v>7136875</v>
+        <v>7136772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,13 +1413,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1438,42 +1442,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131742131</v>
+        <v>131743394</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769833</v>
+        <v>769961</v>
       </c>
       <c r="R9" t="n">
-        <v>7136772</v>
+        <v>7136875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,17 +1523,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131742307</v>
+        <v>131742854</v>
       </c>
       <c r="B19" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,31 +2534,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2566,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769860</v>
+        <v>769873</v>
       </c>
       <c r="R19" t="n">
-        <v>7136813</v>
+        <v>7136797</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,17 +2603,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>hå hackade i död gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2633,7 +2628,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131742285</v>
+        <v>131742307</v>
       </c>
       <c r="B20" t="n">
         <v>57945</v>
@@ -2666,7 +2661,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2676,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769857</v>
+        <v>769860</v>
       </c>
       <c r="R20" t="n">
-        <v>7136809</v>
+        <v>7136813</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,7 +2711,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>hack i basen på gran</t>
+          <t>hå hackade i död gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131742854</v>
+        <v>131742285</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2754,30 +2749,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769873</v>
+        <v>769857</v>
       </c>
       <c r="R21" t="n">
-        <v>7136797</v>
+        <v>7136809</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,13 +2819,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>hack i basen på gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3058,42 +3058,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131741841</v>
+        <v>131743102</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3101,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769719</v>
+        <v>769921</v>
       </c>
       <c r="R24" t="n">
-        <v>7136723</v>
+        <v>7136855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,17 +3138,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3168,41 +3163,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131743102</v>
+        <v>131742542</v>
       </c>
       <c r="B25" t="n">
-        <v>91855</v>
+        <v>57945</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3210,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769921</v>
+        <v>769868</v>
       </c>
       <c r="R25" t="n">
-        <v>7136855</v>
+        <v>7136747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,13 +3244,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hack i rotben på gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3273,42 +3273,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131742542</v>
+        <v>131742606</v>
       </c>
       <c r="B26" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769868</v>
+        <v>769809</v>
       </c>
       <c r="R26" t="n">
-        <v>7136747</v>
+        <v>7136745</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>hack i rotben på gran</t>
+          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,6 +3365,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3383,42 +3384,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131742606</v>
+        <v>131741841</v>
       </c>
       <c r="B27" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3426,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>769809</v>
+        <v>769719</v>
       </c>
       <c r="R27" t="n">
-        <v>7136745</v>
+        <v>7136723</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3467,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>liten förekomst av ca 30x30cm med bladrosetter</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,7 +3476,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
